--- a/enhancements/test-files/03_ARR_pc0101_2026_Aug_reordered.xlsx
+++ b/enhancements/test-files/03_ARR_pc0101_2026_Aug_reordered.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:P6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -432,6 +432,13 @@
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="22" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -480,6 +487,41 @@
           <t>Policy Effective Date</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionPct</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ProducerCommissionAmount</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>CommissionPct</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>GrossCommissionAmount</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Transaction Detail</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>MarketProvider</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -496,11 +538,11 @@
         <v>101</v>
       </c>
       <c r="D2" t="n">
-        <v>23350.39</v>
+        <v>8329.780000000001</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -515,7 +557,32 @@
         <v>46241</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>45997</v>
+        <v>46183</v>
+      </c>
+      <c r="J2" t="n">
+        <v>349.85</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="L2" t="n">
+        <v>649.72</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N2" t="n">
+        <v>999.5700000000001</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Specialty</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -533,26 +600,51 @@
         <v>101</v>
       </c>
       <c r="D3" t="n">
-        <v>15417</v>
+        <v>5635.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Heritage Casualty Co</t>
+          <t>National Indemnity Co</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Apex Insurance Brokers</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>46244</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>46228</v>
+        <v>46165</v>
+      </c>
+      <c r="J3" t="n">
+        <v>256.98</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.07439999999999999</v>
+      </c>
+      <c r="L3" t="n">
+        <v>419.27</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N3" t="n">
+        <v>676.25</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Admitted</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -570,16 +662,16 @@
         <v>101</v>
       </c>
       <c r="D4" t="n">
-        <v>15655.48</v>
+        <v>4905.35</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zenith Insurance Group</t>
+          <t>Heritage Casualty Co</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Pinnacle Agency Partners</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
@@ -589,7 +681,32 @@
         <v>46247</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>45990</v>
+        <v>46052</v>
+      </c>
+      <c r="J4" t="n">
+        <v>182.48</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.0828</v>
+      </c>
+      <c r="L4" t="n">
+        <v>406.16</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N4" t="n">
+        <v>588.64</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>New Business</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lloyd's</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -607,26 +724,51 @@
         <v>101</v>
       </c>
       <c r="D5" t="n">
-        <v>13780.87</v>
+        <v>24749.08</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Liberty Mutual</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Coastal Risk Advisors</t>
+          <t>Metro Agency Group</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46245</v>
+        <v>46250</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>46250</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>46180</v>
+        <v>45971</v>
+      </c>
+      <c r="J5" t="n">
+        <v>1277.05</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="L5" t="n">
+        <v>1692.84</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2969.89</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Endorsement</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -644,16 +786,16 @@
         <v>101</v>
       </c>
       <c r="D6" t="n">
-        <v>16782.44</v>
+        <v>15087.72</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>National Indemnity Co</t>
+          <t>Global Assurance Corp</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Metro Agency Group</t>
+          <t>Brown &amp; Brown</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
@@ -663,7 +805,32 @@
         <v>46253</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>46195</v>
+        <v>46234</v>
+      </c>
+      <c r="J6" t="n">
+        <v>814.74</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="L6" t="n">
+        <v>995.79</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1810.53</v>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Renewal</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Excess &amp; Surplus</t>
+        </is>
       </c>
     </row>
   </sheetData>
